--- a/Power_BI_32h/Aula 5/DashBoard RH/RH Base de dados_v1.xlsx
+++ b/Power_BI_32h/Aula 5/DashBoard RH/RH Base de dados_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://empowerdatasolutions.sharepoint.com/sites/ProducaoConteudo/Documentos Compartilhados/1 - Power BI/1 - Youtube/19 - Dashboard RH/0 - Material Live 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\Documents\GitHub\SENAI2025_Luis\Power_BI_32h\Aula 5\DashBoard RH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{B7686B94-C802-4410-B44A-B992537D45A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ADD861E-2F97-4AFA-85EA-C3E34443EAF1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E834BA1-6B00-4C36-B6E9-9E38BB8586B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-72" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="integrantes" sheetId="6" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="461">
   <si>
     <t>F</t>
   </si>
@@ -1379,6 +1379,33 @@
   </si>
   <si>
     <t>Faixa de Idade</t>
+  </si>
+  <si>
+    <t>Robson Bacchin</t>
+  </si>
+  <si>
+    <t>A1301052300</t>
+  </si>
+  <si>
+    <t>Inativo</t>
+  </si>
+  <si>
+    <t>Reenye Lima</t>
+  </si>
+  <si>
+    <t>A1501052301</t>
+  </si>
+  <si>
+    <t>Wellington Martins</t>
+  </si>
+  <si>
+    <t>A1501052322</t>
+  </si>
+  <si>
+    <t>Luis Fernando</t>
+  </si>
+  <si>
+    <t>A15010523221</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1418,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1531,6 +1558,12 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1946,9 +1979,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1986,7 +2019,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2092,7 +2125,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2234,7 +2267,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2242,22 +2275,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7FBB827-4483-46E1-B977-B741481D7925}">
-  <dimension ref="A1:J208"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J212"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>220</v>
       </c>
@@ -2289,7 +2322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>79</v>
       </c>
@@ -2321,7 +2354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>84</v>
       </c>
@@ -2353,7 +2386,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>85</v>
       </c>
@@ -2385,7 +2418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>86</v>
       </c>
@@ -2417,7 +2450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>80</v>
       </c>
@@ -2449,7 +2482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>82</v>
       </c>
@@ -2481,7 +2514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>428</v>
       </c>
@@ -2513,7 +2546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>88</v>
       </c>
@@ -2545,7 +2578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>92</v>
       </c>
@@ -2577,7 +2610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>90</v>
       </c>
@@ -2609,7 +2642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>91</v>
       </c>
@@ -2641,7 +2674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>93</v>
       </c>
@@ -2673,7 +2706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>96</v>
       </c>
@@ -2705,7 +2738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>95</v>
       </c>
@@ -2737,7 +2770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
@@ -2769,7 +2802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>98</v>
       </c>
@@ -2801,7 +2834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>99</v>
       </c>
@@ -2833,7 +2866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>100</v>
       </c>
@@ -2865,7 +2898,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>104</v>
       </c>
@@ -2897,7 +2930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>101</v>
       </c>
@@ -2929,7 +2962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>102</v>
       </c>
@@ -2961,7 +2994,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>106</v>
       </c>
@@ -2993,7 +3026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>103</v>
       </c>
@@ -3025,7 +3058,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>108</v>
       </c>
@@ -3057,7 +3090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -3089,7 +3122,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>105</v>
       </c>
@@ -3121,7 +3154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>110</v>
       </c>
@@ -3153,7 +3186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>113</v>
       </c>
@@ -3185,7 +3218,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>115</v>
       </c>
@@ -3217,7 +3250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>116</v>
       </c>
@@ -3249,7 +3282,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>118</v>
       </c>
@@ -3281,7 +3314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>120</v>
       </c>
@@ -3313,7 +3346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>122</v>
       </c>
@@ -3345,7 +3378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>107</v>
       </c>
@@ -3377,7 +3410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>128</v>
       </c>
@@ -3409,7 +3442,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>129</v>
       </c>
@@ -3441,7 +3474,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>131</v>
       </c>
@@ -3473,7 +3506,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
@@ -3505,7 +3538,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>111</v>
       </c>
@@ -3537,7 +3570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>132</v>
       </c>
@@ -3569,7 +3602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>112</v>
       </c>
@@ -3601,7 +3634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>114</v>
       </c>
@@ -3633,7 +3666,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>134</v>
       </c>
@@ -3665,7 +3698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>135</v>
       </c>
@@ -3697,7 +3730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>117</v>
       </c>
@@ -3729,7 +3762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>119</v>
       </c>
@@ -3761,7 +3794,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>121</v>
       </c>
@@ -3793,7 +3826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>123</v>
       </c>
@@ -3825,7 +3858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>140</v>
       </c>
@@ -3857,7 +3890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>141</v>
       </c>
@@ -3889,7 +3922,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>124</v>
       </c>
@@ -3921,7 +3954,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>143</v>
       </c>
@@ -3953,7 +3986,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>145</v>
       </c>
@@ -3985,7 +4018,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>125</v>
       </c>
@@ -4017,7 +4050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>126</v>
       </c>
@@ -4049,7 +4082,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>147</v>
       </c>
@@ -4081,7 +4114,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>75</v>
       </c>
@@ -4113,7 +4146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>43</v>
       </c>
@@ -4145,7 +4178,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>130</v>
       </c>
@@ -4177,7 +4210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>169</v>
       </c>
@@ -4209,7 +4242,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>170</v>
       </c>
@@ -4241,7 +4274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>171</v>
       </c>
@@ -4273,7 +4306,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>133</v>
       </c>
@@ -4305,7 +4338,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>172</v>
       </c>
@@ -4337,7 +4370,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>173</v>
       </c>
@@ -4369,7 +4402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>174</v>
       </c>
@@ -4401,7 +4434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>175</v>
       </c>
@@ -4433,7 +4466,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>137</v>
       </c>
@@ -4465,7 +4498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>176</v>
       </c>
@@ -4497,7 +4530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>139</v>
       </c>
@@ -4529,7 +4562,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
@@ -4561,7 +4594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>177</v>
       </c>
@@ -4593,7 +4626,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
@@ -4625,7 +4658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>178</v>
       </c>
@@ -4657,7 +4690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>94</v>
       </c>
@@ -4689,7 +4722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>97</v>
       </c>
@@ -4721,7 +4754,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>138</v>
       </c>
@@ -4753,7 +4786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>87</v>
       </c>
@@ -4785,7 +4818,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>8</v>
       </c>
@@ -4817,7 +4850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>127</v>
       </c>
@@ -4849,7 +4882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>167</v>
       </c>
@@ -4881,7 +4914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>168</v>
       </c>
@@ -4913,7 +4946,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>144</v>
       </c>
@@ -4945,7 +4978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>179</v>
       </c>
@@ -4977,7 +5010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>21</v>
       </c>
@@ -5009,7 +5042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>22</v>
       </c>
@@ -5041,7 +5074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>18</v>
       </c>
@@ -5073,7 +5106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -5105,7 +5138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>20</v>
       </c>
@@ -5137,7 +5170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>23</v>
       </c>
@@ -5169,7 +5202,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>7</v>
       </c>
@@ -5201,7 +5234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>25</v>
       </c>
@@ -5233,7 +5266,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>24</v>
       </c>
@@ -5265,7 +5298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>26</v>
       </c>
@@ -5297,7 +5330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>27</v>
       </c>
@@ -5329,7 +5362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>29</v>
       </c>
@@ -5361,7 +5394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>28</v>
       </c>
@@ -5393,7 +5426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>31</v>
       </c>
@@ -5425,7 +5458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>30</v>
       </c>
@@ -5457,7 +5490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>33</v>
       </c>
@@ -5489,7 +5522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>35</v>
       </c>
@@ -5521,7 +5554,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>37</v>
       </c>
@@ -5553,7 +5586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>39</v>
       </c>
@@ -5585,7 +5618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>32</v>
       </c>
@@ -5617,7 +5650,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>34</v>
       </c>
@@ -5649,7 +5682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>36</v>
       </c>
@@ -5681,7 +5714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>41</v>
       </c>
@@ -5713,7 +5746,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>38</v>
       </c>
@@ -5745,7 +5778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>54</v>
       </c>
@@ -5777,7 +5810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,7 +5842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>70</v>
       </c>
@@ -5841,7 +5874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>6</v>
       </c>
@@ -5873,7 +5906,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>77</v>
       </c>
@@ -5905,7 +5938,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>72</v>
       </c>
@@ -5937,7 +5970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>78</v>
       </c>
@@ -5969,7 +6002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>73</v>
       </c>
@@ -6001,7 +6034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>81</v>
       </c>
@@ -6033,7 +6066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>76</v>
       </c>
@@ -6065,7 +6098,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>83</v>
       </c>
@@ -6097,7 +6130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>142</v>
       </c>
@@ -6129,7 +6162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>180</v>
       </c>
@@ -6161,7 +6194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>181</v>
       </c>
@@ -6193,7 +6226,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>182</v>
       </c>
@@ -6225,7 +6258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>183</v>
       </c>
@@ -6257,7 +6290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>148</v>
       </c>
@@ -6289,7 +6322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>184</v>
       </c>
@@ -6321,7 +6354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>185</v>
       </c>
@@ -6353,7 +6386,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>186</v>
       </c>
@@ -6385,7 +6418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>187</v>
       </c>
@@ -6417,7 +6450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>188</v>
       </c>
@@ -6449,7 +6482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>43</v>
       </c>
@@ -6481,7 +6514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>189</v>
       </c>
@@ -6513,7 +6546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>149</v>
       </c>
@@ -6545,7 +6578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>150</v>
       </c>
@@ -6577,7 +6610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>151</v>
       </c>
@@ -6609,7 +6642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>152</v>
       </c>
@@ -6641,7 +6674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>153</v>
       </c>
@@ -6673,7 +6706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>190</v>
       </c>
@@ -6705,7 +6738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>191</v>
       </c>
@@ -6737,7 +6770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>154</v>
       </c>
@@ -6769,7 +6802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>155</v>
       </c>
@@ -6801,7 +6834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>192</v>
       </c>
@@ -6833,7 +6866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>193</v>
       </c>
@@ -6865,7 +6898,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>156</v>
       </c>
@@ -6897,7 +6930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>194</v>
       </c>
@@ -6929,7 +6962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>211</v>
       </c>
@@ -6961,7 +6994,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>157</v>
       </c>
@@ -6993,7 +7026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>158</v>
       </c>
@@ -7025,7 +7058,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>195</v>
       </c>
@@ -7057,7 +7090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>196</v>
       </c>
@@ -7089,7 +7122,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>197</v>
       </c>
@@ -7121,7 +7154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>198</v>
       </c>
@@ -7153,7 +7186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>43</v>
       </c>
@@ -7185,7 +7218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>161</v>
       </c>
@@ -7217,7 +7250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>14</v>
       </c>
@@ -7249,7 +7282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>15</v>
       </c>
@@ -7281,7 +7314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>16</v>
       </c>
@@ -7313,7 +7346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>17</v>
       </c>
@@ -7345,7 +7378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>40</v>
       </c>
@@ -7377,7 +7410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>43</v>
       </c>
@@ -7409,7 +7442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>45</v>
       </c>
@@ -7441,7 +7474,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>46</v>
       </c>
@@ -7473,7 +7506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>47</v>
       </c>
@@ -7505,7 +7538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>42</v>
       </c>
@@ -7537,7 +7570,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>44</v>
       </c>
@@ -7569,7 +7602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>48</v>
       </c>
@@ -7601,7 +7634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>136</v>
       </c>
@@ -7633,7 +7666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>49</v>
       </c>
@@ -7665,7 +7698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>50</v>
       </c>
@@ -7697,7 +7730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>51</v>
       </c>
@@ -7729,7 +7762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>52</v>
       </c>
@@ -7761,7 +7794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>55</v>
       </c>
@@ -7793,7 +7826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>53</v>
       </c>
@@ -7825,7 +7858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>57</v>
       </c>
@@ -7857,7 +7890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>59</v>
       </c>
@@ -7889,7 +7922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>62</v>
       </c>
@@ -7921,7 +7954,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>64</v>
       </c>
@@ -7953,7 +7986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>65</v>
       </c>
@@ -7985,7 +8018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>58</v>
       </c>
@@ -8017,7 +8050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>60</v>
       </c>
@@ -8049,7 +8082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>61</v>
       </c>
@@ -8081,7 +8114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>67</v>
       </c>
@@ -8113,7 +8146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>69</v>
       </c>
@@ -8145,7 +8178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>63</v>
       </c>
@@ -8177,7 +8210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>94</v>
       </c>
@@ -8209,7 +8242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>71</v>
       </c>
@@ -8241,7 +8274,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>66</v>
       </c>
@@ -8273,7 +8306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>68</v>
       </c>
@@ -8305,7 +8338,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>74</v>
       </c>
@@ -8337,7 +8370,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>199</v>
       </c>
@@ -8369,7 +8402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>159</v>
       </c>
@@ -8401,7 +8434,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>160</v>
       </c>
@@ -8433,7 +8466,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>200</v>
       </c>
@@ -8465,7 +8498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>201</v>
       </c>
@@ -8497,7 +8530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>202</v>
       </c>
@@ -8529,7 +8562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>203</v>
       </c>
@@ -8561,7 +8594,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>204</v>
       </c>
@@ -8593,7 +8626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>162</v>
       </c>
@@ -8625,7 +8658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>163</v>
       </c>
@@ -8657,7 +8690,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>205</v>
       </c>
@@ -8689,7 +8722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>206</v>
       </c>
@@ -8721,7 +8754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>207</v>
       </c>
@@ -8753,7 +8786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>208</v>
       </c>
@@ -8785,7 +8818,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>164</v>
       </c>
@@ -8817,7 +8850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>165</v>
       </c>
@@ -8849,7 +8882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>166</v>
       </c>
@@ -8881,7 +8914,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>209</v>
       </c>
@@ -8913,8 +8946,137 @@
         <v>11</v>
       </c>
     </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C209" s="5">
+        <v>8500</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E209" s="3">
+        <v>35</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H209" s="2">
+        <v>43188</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C210" s="5">
+        <v>12000</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E210" s="3">
+        <v>33</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H210" s="2">
+        <v>43188</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C211" s="5">
+        <v>8500</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E211" s="3">
+        <v>46</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H211" s="2">
+        <v>43188</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C212" s="5">
+        <v>1804</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E212" s="3">
+        <v>31</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H212" s="2">
+        <v>43188</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J208" xr:uid="{D7FBB827-4483-46E1-B977-B741481D7925}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
